--- a/03_Outputs/all/01_TablasDescriptivas/idx1_servicio_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx1_servicio_vr.xlsx
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.019750118316065</v>
+        <v>1.019750118316068</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>2.855828690836422</v>
+        <v>2.855828690836424</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>2.999999999999997</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>61.20261908401194</v>
+        <v>61.20261908401188</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>33.99167061053554</v>
+        <v>33.99167061053559</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>4.805710305452529</v>
+        <v>4.805710305452526</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>61.20261908401194</v>
+        <v>61.20261908401188</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>95.19428969454748</v>
+        <v>95.19428969454746</v>
       </c>
       <c r="C12">
         <v>2</v>
